--- a/excel1.xlsx
+++ b/excel1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git_12-28-26\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git_clone1\git.12-08-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06C6AA76-9797-4068-BF41-16CC1014D282}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C6B75E5-265C-45B1-BDF5-B623D182A30E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,12 +25,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Date</t>
   </si>
   <si>
     <t>Time</t>
+  </si>
+  <si>
+    <t>7:15am</t>
   </si>
 </sst>
 </file>
@@ -81,9 +84,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -381,8 +385,12 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="5:8" x14ac:dyDescent="0.35">
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
+      <c r="E4" s="2">
+        <v>46246</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
     </row>
